--- a/Test_Data/DimPlayers.xlsx
+++ b/Test_Data/DimPlayers.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55cd0139eebd0c53/Desktop/Github Repo/PaupackLaxStatTracking/Test_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_84652279CAB387D3A6F3914ACC38CDB9A21CB009" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B13D6E63-A7A0-4587-BF08-77B0D2EB79F5}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_84652279CAB387D3A6F3914ACC38CDB9A21CB009" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F39117A9-76DE-4BB2-B3F6-AA58EA7849B9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DimPlayers" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -172,6 +185,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Test_Data/DimPlayers.xlsx
+++ b/Test_Data/DimPlayers.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="11_84652279CAB387D3A6F3914ACC38CDB9A21CB009" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F39117A9-76DE-4BB2-B3F6-AA58EA7849B9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5010" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DimPlayers" sheetId="1" r:id="rId1"/>
